--- a/Analysis/tables/B5_vif.xlsx
+++ b/Analysis/tables/B5_vif.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.58</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.63</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.15</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.55</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,47 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.62</v>
+        <v>19.32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>team_early_cs_10</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>team_early_gold_adv</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>team_early_takedowns</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>avg_skill_index</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
